--- a/config/Ajio_instruction.xlsx
+++ b/config/Ajio_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1C1E4C-1CE7-4E3C-BB0F-E98A8CFDD96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA36D6CA-2E31-4E09-97E5-DE4B668E4AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="135">
   <si>
     <t>Base file Column</t>
   </si>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>Ajio Template Column</t>
+  </si>
+  <si>
+    <t>Tshirts</t>
   </si>
 </sst>
 </file>
@@ -844,6 +847,9 @@
       <c r="B2" t="s">
         <v>44</v>
       </c>
+      <c r="C2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -852,6 +858,9 @@
       <c r="B3" t="s">
         <v>45</v>
       </c>
+      <c r="C3" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -860,6 +869,9 @@
       <c r="B4" t="s">
         <v>46</v>
       </c>
+      <c r="C4" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -868,6 +880,9 @@
       <c r="B5" t="s">
         <v>47</v>
       </c>
+      <c r="C5" t="s">
+        <v>134</v>
+      </c>
       <c r="D5" t="s">
         <v>2</v>
       </c>
@@ -879,11 +894,17 @@
       <c r="B6" t="s">
         <v>48</v>
       </c>
+      <c r="C6" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>49</v>
       </c>
+      <c r="C7" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -892,6 +913,9 @@
       <c r="B8" t="s">
         <v>50</v>
       </c>
+      <c r="C8" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -900,6 +924,9 @@
       <c r="B9" t="s">
         <v>51</v>
       </c>
+      <c r="C9" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -908,6 +935,9 @@
       <c r="B10" t="s">
         <v>52</v>
       </c>
+      <c r="C10" t="s">
+        <v>134</v>
+      </c>
       <c r="D10" t="s">
         <v>2</v>
       </c>
@@ -919,6 +949,9 @@
       <c r="B11" t="s">
         <v>53</v>
       </c>
+      <c r="C11" t="s">
+        <v>134</v>
+      </c>
       <c r="D11" t="s">
         <v>2</v>
       </c>
@@ -930,6 +963,9 @@
       <c r="B12" t="s">
         <v>54</v>
       </c>
+      <c r="C12" t="s">
+        <v>134</v>
+      </c>
       <c r="D12" t="s">
         <v>2</v>
       </c>
@@ -941,6 +977,9 @@
       <c r="B13" t="s">
         <v>55</v>
       </c>
+      <c r="C13" t="s">
+        <v>134</v>
+      </c>
       <c r="D13" t="s">
         <v>2</v>
       </c>
@@ -952,6 +991,9 @@
       <c r="B14" t="s">
         <v>56</v>
       </c>
+      <c r="C14" t="s">
+        <v>134</v>
+      </c>
       <c r="D14" t="s">
         <v>2</v>
       </c>
@@ -960,61 +1002,97 @@
       <c r="B15" t="s">
         <v>57</v>
       </c>
+      <c r="C15" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>58</v>
       </c>
+      <c r="C16" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>59</v>
       </c>
+      <c r="C17" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>60</v>
       </c>
+      <c r="C18" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>61</v>
       </c>
+      <c r="C19" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>62</v>
       </c>
+      <c r="C20" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>63</v>
       </c>
+      <c r="C21" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>64</v>
       </c>
+      <c r="C22" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>65</v>
       </c>
+      <c r="C23" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>66</v>
       </c>
+      <c r="C24" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>67</v>
       </c>
+      <c r="C25" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>68</v>
       </c>
+      <c r="C26" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
@@ -1023,6 +1101,9 @@
       <c r="B27" t="s">
         <v>69</v>
       </c>
+      <c r="C27" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
@@ -1031,6 +1112,9 @@
       <c r="B28" t="s">
         <v>70</v>
       </c>
+      <c r="C28" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
@@ -1039,6 +1123,9 @@
       <c r="B29" t="s">
         <v>71</v>
       </c>
+      <c r="C29" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
@@ -1047,6 +1134,9 @@
       <c r="B30" t="s">
         <v>7</v>
       </c>
+      <c r="C30" t="s">
+        <v>134</v>
+      </c>
       <c r="D30" t="s">
         <v>2</v>
       </c>
@@ -1058,6 +1148,9 @@
       <c r="B31" t="s">
         <v>72</v>
       </c>
+      <c r="C31" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
@@ -1066,11 +1159,17 @@
       <c r="B32" t="s">
         <v>73</v>
       </c>
+      <c r="C32" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>74</v>
       </c>
+      <c r="C33" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
@@ -1079,11 +1178,17 @@
       <c r="B34" t="s">
         <v>75</v>
       </c>
+      <c r="C34" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>76</v>
       </c>
+      <c r="C35" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
@@ -1092,6 +1197,9 @@
       <c r="B36" t="s">
         <v>77</v>
       </c>
+      <c r="C36" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
@@ -1100,6 +1208,9 @@
       <c r="B37" t="s">
         <v>78</v>
       </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
@@ -1108,6 +1219,9 @@
       <c r="B38" t="s">
         <v>79</v>
       </c>
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
       <c r="D38" t="s">
         <v>2</v>
       </c>
@@ -1116,25 +1230,43 @@
       <c r="B39" t="s">
         <v>80</v>
       </c>
+      <c r="C39" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>81</v>
       </c>
+      <c r="C40" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>82</v>
       </c>
+      <c r="C41" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>83</v>
       </c>
+      <c r="C42" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>27</v>
+      </c>
       <c r="B43" t="s">
         <v>84</v>
+      </c>
+      <c r="C43" t="s">
+        <v>134</v>
       </c>
       <c r="D43" t="s">
         <v>2</v>
@@ -1147,26 +1279,41 @@
       <c r="B44" t="s">
         <v>85</v>
       </c>
+      <c r="C44" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>86</v>
       </c>
+      <c r="C45" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>87</v>
       </c>
+      <c r="C46" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>88</v>
       </c>
+      <c r="C47" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>89</v>
       </c>
+      <c r="C48" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
@@ -1175,6 +1322,9 @@
       <c r="B49" t="s">
         <v>90</v>
       </c>
+      <c r="C49" t="s">
+        <v>134</v>
+      </c>
       <c r="D49" t="s">
         <v>2</v>
       </c>
@@ -1183,11 +1333,17 @@
       <c r="B50" t="s">
         <v>91</v>
       </c>
+      <c r="C50" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>92</v>
       </c>
+      <c r="C51" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
@@ -1196,6 +1352,9 @@
       <c r="B52" t="s">
         <v>93</v>
       </c>
+      <c r="C52" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
@@ -1204,6 +1363,9 @@
       <c r="B53" t="s">
         <v>94</v>
       </c>
+      <c r="C53" t="s">
+        <v>134</v>
+      </c>
       <c r="D53" t="s">
         <v>2</v>
       </c>
@@ -1215,6 +1377,9 @@
       <c r="B54" t="s">
         <v>95</v>
       </c>
+      <c r="C54" t="s">
+        <v>134</v>
+      </c>
       <c r="D54" t="s">
         <v>2</v>
       </c>
@@ -1226,11 +1391,17 @@
       <c r="B55" t="s">
         <v>96</v>
       </c>
+      <c r="C55" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>35</v>
       </c>
+      <c r="C56" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
@@ -1239,6 +1410,9 @@
       <c r="B57" t="s">
         <v>97</v>
       </c>
+      <c r="C57" t="s">
+        <v>134</v>
+      </c>
       <c r="D57" t="s">
         <v>2</v>
       </c>
@@ -1250,6 +1424,9 @@
       <c r="B58" t="s">
         <v>98</v>
       </c>
+      <c r="C58" t="s">
+        <v>134</v>
+      </c>
       <c r="D58" t="s">
         <v>2</v>
       </c>
@@ -1261,6 +1438,9 @@
       <c r="B59" t="s">
         <v>99</v>
       </c>
+      <c r="C59" t="s">
+        <v>134</v>
+      </c>
       <c r="D59" t="s">
         <v>2</v>
       </c>
@@ -1269,21 +1449,33 @@
       <c r="B60" t="s">
         <v>100</v>
       </c>
+      <c r="C60" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>101</v>
       </c>
+      <c r="C61" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>102</v>
       </c>
+      <c r="C62" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>103</v>
       </c>
+      <c r="C63" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
@@ -1292,6 +1484,9 @@
       <c r="B64" t="s">
         <v>104</v>
       </c>
+      <c r="C64" t="s">
+        <v>134</v>
+      </c>
       <c r="D64" t="s">
         <v>2</v>
       </c>
@@ -1300,6 +1495,9 @@
       <c r="B65" t="s">
         <v>105</v>
       </c>
+      <c r="C65" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
@@ -1308,6 +1506,9 @@
       <c r="B66" t="s">
         <v>106</v>
       </c>
+      <c r="C66" t="s">
+        <v>134</v>
+      </c>
       <c r="D66" t="s">
         <v>2</v>
       </c>
@@ -1319,6 +1520,9 @@
       <c r="B67" t="s">
         <v>107</v>
       </c>
+      <c r="C67" t="s">
+        <v>134</v>
+      </c>
       <c r="D67" t="s">
         <v>2</v>
       </c>
@@ -1330,6 +1534,9 @@
       <c r="B68" t="s">
         <v>108</v>
       </c>
+      <c r="C68" t="s">
+        <v>134</v>
+      </c>
       <c r="D68" t="s">
         <v>2</v>
       </c>
@@ -1341,6 +1548,9 @@
       <c r="B69" t="s">
         <v>109</v>
       </c>
+      <c r="C69" t="s">
+        <v>134</v>
+      </c>
       <c r="D69" t="s">
         <v>2</v>
       </c>
@@ -1352,6 +1562,9 @@
       <c r="B70" t="s">
         <v>110</v>
       </c>
+      <c r="C70" t="s">
+        <v>134</v>
+      </c>
       <c r="D70" t="s">
         <v>2</v>
       </c>
@@ -1360,6 +1573,9 @@
       <c r="B71" t="s">
         <v>22</v>
       </c>
+      <c r="C71" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
@@ -1368,6 +1584,9 @@
       <c r="B72" t="s">
         <v>10</v>
       </c>
+      <c r="C72" t="s">
+        <v>134</v>
+      </c>
       <c r="D72" t="s">
         <v>2</v>
       </c>
@@ -1379,13 +1598,22 @@
       <c r="B73" t="s">
         <v>111</v>
       </c>
+      <c r="C73" t="s">
+        <v>134</v>
+      </c>
       <c r="D73" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>23</v>
+      </c>
       <c r="B74" t="s">
         <v>112</v>
+      </c>
+      <c r="C74" t="s">
+        <v>134</v>
       </c>
       <c r="D74" t="s">
         <v>2</v>
@@ -1398,6 +1626,9 @@
       <c r="B75" t="s">
         <v>5</v>
       </c>
+      <c r="C75" t="s">
+        <v>134</v>
+      </c>
       <c r="D75" t="s">
         <v>2</v>
       </c>
@@ -1409,6 +1640,9 @@
       <c r="B76" t="s">
         <v>113</v>
       </c>
+      <c r="C76" t="s">
+        <v>134</v>
+      </c>
       <c r="D76" t="s">
         <v>2</v>
       </c>
@@ -1417,6 +1651,9 @@
       <c r="B77" t="s">
         <v>12</v>
       </c>
+      <c r="C77" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
@@ -1425,6 +1662,9 @@
       <c r="B78" t="s">
         <v>114</v>
       </c>
+      <c r="C78" t="s">
+        <v>134</v>
+      </c>
       <c r="D78" t="s">
         <v>2</v>
       </c>
@@ -1433,120 +1673,174 @@
       <c r="B79" t="s">
         <v>115</v>
       </c>
+      <c r="C79" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C80" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C81" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>28</v>
       </c>
       <c r="B82" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C82" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>29</v>
       </c>
       <c r="B83" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C83" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>30</v>
       </c>
       <c r="B84" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C84" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>31</v>
       </c>
       <c r="B85" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C85" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>32</v>
       </c>
       <c r="B86" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C86" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>33</v>
       </c>
       <c r="B87" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C87" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>34</v>
       </c>
       <c r="B88" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C88" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>41</v>
       </c>
       <c r="B89" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C89" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>42</v>
       </c>
       <c r="B90" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C90" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>43</v>
       </c>
       <c r="B91" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C91" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C92" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C93" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C94" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C95" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>132</v>
+      </c>
+      <c r="C96" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/config/Ajio_instruction.xlsx
+++ b/config/Ajio_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA36D6CA-2E31-4E09-97E5-DE4B668E4AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3025E25-BF00-4A04-A025-01B08C201526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
         <v>84</v>

--- a/config/Ajio_instruction.xlsx
+++ b/config/Ajio_instruction.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3025E25-BF00-4A04-A025-01B08C201526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D89126F-238A-49D4-98CD-30CD3AF7990A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="1" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mapping-Tshirts" sheetId="6" r:id="rId1"/>
+    <sheet name="Mapping-Tshirts" sheetId="7" r:id="rId1"/>
+    <sheet name="Mapping-Kids Tshirts" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping-Tshirts'!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Kids Tshirts'!$A$1:$F$89</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="139">
   <si>
     <t>Base file Column</t>
   </si>
@@ -65,9 +66,6 @@
     <t>Character</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
     <t>Final Category</t>
   </si>
   <si>
@@ -444,6 +442,21 @@
   </si>
   <si>
     <t>Tshirts</t>
+  </si>
+  <si>
+    <t>Feature Detail</t>
+  </si>
+  <si>
+    <t>*Sleeve</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Kids Tshirts</t>
+  </si>
+  <si>
+    <t>Ajio Category</t>
   </si>
 </sst>
 </file>
@@ -814,432 +827,1450 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA3588D-D2B2-48C0-90F8-D1F1ED2FADB8}">
+  <dimension ref="A1:D96"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" t="s">
+        <v>133</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>85</v>
+      </c>
+      <c r="C45" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" t="s">
+        <v>133</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" t="s">
+        <v>133</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" t="s">
+        <v>133</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" t="s">
+        <v>133</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B61" t="s">
+        <v>100</v>
+      </c>
+      <c r="C61" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" t="s">
+        <v>103</v>
+      </c>
+      <c r="C64" t="s">
+        <v>133</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>104</v>
+      </c>
+      <c r="C65" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" t="s">
+        <v>133</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" t="s">
+        <v>133</v>
+      </c>
+      <c r="D67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>24</v>
+      </c>
+      <c r="B69" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" t="s">
+        <v>133</v>
+      </c>
+      <c r="D69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" t="s">
+        <v>109</v>
+      </c>
+      <c r="C70" t="s">
+        <v>133</v>
+      </c>
+      <c r="D70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" t="s">
+        <v>133</v>
+      </c>
+      <c r="D72" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" t="s">
+        <v>110</v>
+      </c>
+      <c r="C73" t="s">
+        <v>133</v>
+      </c>
+      <c r="D73" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C74" t="s">
+        <v>133</v>
+      </c>
+      <c r="D74" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" t="s">
+        <v>133</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76" t="s">
+        <v>112</v>
+      </c>
+      <c r="C76" t="s">
+        <v>133</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" t="s">
+        <v>113</v>
+      </c>
+      <c r="C78" t="s">
+        <v>133</v>
+      </c>
+      <c r="D78" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>114</v>
+      </c>
+      <c r="C79" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>115</v>
+      </c>
+      <c r="C80" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>116</v>
+      </c>
+      <c r="C81" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>27</v>
+      </c>
+      <c r="B82" t="s">
+        <v>117</v>
+      </c>
+      <c r="C82" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>28</v>
+      </c>
+      <c r="B83" t="s">
+        <v>118</v>
+      </c>
+      <c r="C83" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>29</v>
+      </c>
+      <c r="B84" t="s">
+        <v>119</v>
+      </c>
+      <c r="C84" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
+        <v>120</v>
+      </c>
+      <c r="C85" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>31</v>
+      </c>
+      <c r="B86" t="s">
+        <v>121</v>
+      </c>
+      <c r="C86" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>32</v>
+      </c>
+      <c r="B87" t="s">
+        <v>122</v>
+      </c>
+      <c r="C87" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B88" t="s">
+        <v>123</v>
+      </c>
+      <c r="C88" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" t="s">
+        <v>124</v>
+      </c>
+      <c r="C89" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" t="s">
+        <v>125</v>
+      </c>
+      <c r="C90" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>42</v>
+      </c>
+      <c r="B91" t="s">
+        <v>126</v>
+      </c>
+      <c r="C91" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B92" t="s">
+        <v>127</v>
+      </c>
+      <c r="C92" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B93" t="s">
+        <v>128</v>
+      </c>
+      <c r="C93" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B94" t="s">
+        <v>129</v>
+      </c>
+      <c r="C94" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B95" t="s">
+        <v>130</v>
+      </c>
+      <c r="C95" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B96" t="s">
+        <v>131</v>
+      </c>
+      <c r="C96" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F62085-80E4-4F8B-99A1-7536229413A5}">
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>138</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>45</v>
       </c>
-      <c r="C3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>46</v>
       </c>
-      <c r="C4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>47</v>
       </c>
-      <c r="C5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
         <v>48</v>
       </c>
-      <c r="C6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>49</v>
-      </c>
       <c r="C7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="C9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>36</v>
       </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" t="s">
-        <v>134</v>
-      </c>
-      <c r="D13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B26" t="s">
+      <c r="B29" t="s">
         <v>68</v>
       </c>
-      <c r="C26" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="C29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>37</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B30" t="s">
         <v>69</v>
       </c>
-      <c r="C27" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="C30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>38</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B31" t="s">
         <v>70</v>
       </c>
-      <c r="C28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="C31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" t="s">
         <v>71</v>
       </c>
-      <c r="C29" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" t="s">
-        <v>134</v>
-      </c>
-      <c r="D30" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="C32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" t="s">
         <v>72</v>
       </c>
-      <c r="C31" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B33" t="s">
-        <v>74</v>
-      </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>40</v>
-      </c>
       <c r="B34" t="s">
         <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
       <c r="B35" t="s">
         <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
         <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>9</v>
-      </c>
       <c r="B38" t="s">
         <v>79</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
-      </c>
-      <c r="D38" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -1247,40 +2278,40 @@
         <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
         <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D43" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -1288,7 +2319,7 @@
         <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -1296,23 +2327,29 @@
         <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>6</v>
+      </c>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -1320,13 +2357,10 @@
         <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
-        <v>134</v>
-      </c>
-      <c r="D49" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -1334,54 +2368,48 @@
         <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>21</v>
-      </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C53" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D53" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>24</v>
-      </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
-      </c>
-      <c r="D54" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
@@ -1389,29 +2417,38 @@
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>23</v>
+      </c>
       <c r="B56" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C57" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D57" t="s">
         <v>2</v>
@@ -1419,95 +2456,113 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C58" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>6</v>
-      </c>
       <c r="B59" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
-      </c>
-      <c r="D59" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>10</v>
+      </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C61" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>7</v>
+      </c>
       <c r="B62" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>21</v>
+      </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="C63" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D64" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>22</v>
+      </c>
       <c r="B65" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C65" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D66" t="s">
         <v>2</v>
@@ -1515,13 +2570,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B67" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D67" t="s">
         <v>2</v>
@@ -1529,13 +2584,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C68" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D68" t="s">
         <v>2</v>
@@ -1543,13 +2598,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D69" t="s">
         <v>2</v>
@@ -1557,13 +2612,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
         <v>110</v>
       </c>
       <c r="C70" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D70" t="s">
         <v>2</v>
@@ -1571,21 +2626,21 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="C71" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D72" t="s">
         <v>2</v>
@@ -1593,254 +2648,174 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="C73" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D73" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>23</v>
-      </c>
       <c r="B74" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
-      </c>
-      <c r="D74" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="C75" t="s">
-        <v>134</v>
-      </c>
-      <c r="D75" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B76" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C76" t="s">
-        <v>134</v>
-      </c>
-      <c r="D76" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>29</v>
+      </c>
       <c r="B77" t="s">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="C77" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B78" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C78" t="s">
-        <v>134</v>
-      </c>
-      <c r="D78" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>31</v>
+      </c>
       <c r="B79" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C79" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>32</v>
+      </c>
       <c r="B80" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>33</v>
+      </c>
       <c r="B81" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C81" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B82" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C82" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C83" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C84" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>31</v>
-      </c>
       <c r="B85" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>32</v>
-      </c>
       <c r="B86" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C86" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>33</v>
-      </c>
       <c r="B87" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C87" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>34</v>
-      </c>
       <c r="B88" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C88" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>41</v>
-      </c>
       <c r="B89" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C89" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>42</v>
-      </c>
-      <c r="B90" t="s">
-        <v>126</v>
-      </c>
-      <c r="C90" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>43</v>
-      </c>
-      <c r="B91" t="s">
-        <v>127</v>
-      </c>
-      <c r="C91" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B92" t="s">
-        <v>128</v>
-      </c>
-      <c r="C92" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B93" t="s">
-        <v>129</v>
-      </c>
-      <c r="C93" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B94" t="s">
-        <v>130</v>
-      </c>
-      <c r="C94" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B95" t="s">
-        <v>131</v>
-      </c>
-      <c r="C95" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B96" t="s">
-        <v>132</v>
-      </c>
-      <c r="C96" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/config/Ajio_instruction.xlsx
+++ b/config/Ajio_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D89126F-238A-49D4-98CD-30CD3AF7990A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDDE051-4FD4-4A7C-96CD-18B76F916117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="1" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>

--- a/config/Ajio_instruction.xlsx
+++ b/config/Ajio_instruction.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDDE051-4FD4-4A7C-96CD-18B76F916117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD88CE17-3FD8-44C7-9504-3727ED755357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="1" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="3" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping-Tshirts" sheetId="7" r:id="rId1"/>
     <sheet name="Mapping-Kids Tshirts" sheetId="6" r:id="rId2"/>
+    <sheet name="Mapping-Boys Sandal" sheetId="8" r:id="rId3"/>
+    <sheet name="Mapping-Boys Shoes" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Kids Tshirts'!$A$1:$F$89</definedName>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="165">
   <si>
     <t>Base file Column</t>
   </si>
@@ -457,6 +459,84 @@
   </si>
   <si>
     <t>Ajio Category</t>
+  </si>
+  <si>
+    <t>MASTER CODE</t>
+  </si>
+  <si>
+    <t>Boys Sandal</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>HSN</t>
+  </si>
+  <si>
+    <t>Size Map</t>
+  </si>
+  <si>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>Imported by/</t>
+  </si>
+  <si>
+    <t>Manufacturer Name and Address with Pincode</t>
+  </si>
+  <si>
+    <t>Marketed By</t>
+  </si>
+  <si>
+    <t>Package Contains</t>
+  </si>
+  <si>
+    <t>Warranty</t>
+  </si>
+  <si>
+    <t>COLOUR</t>
+  </si>
+  <si>
+    <t>Fit Type</t>
+  </si>
+  <si>
+    <t>Collection</t>
+  </si>
+  <si>
+    <t>MaterialInfo/Upper Fabric</t>
+  </si>
+  <si>
+    <t>*Upper Material</t>
+  </si>
+  <si>
+    <t>Sole Material</t>
+  </si>
+  <si>
+    <t>*Sole Material</t>
+  </si>
+  <si>
+    <t>Material Feature</t>
+  </si>
+  <si>
+    <t>Insole Detail</t>
+  </si>
+  <si>
+    <t>*Fastening</t>
+  </si>
+  <si>
+    <t>*Care</t>
+  </si>
+  <si>
+    <t>*Heel</t>
+  </si>
+  <si>
+    <t>*Toe-shape</t>
+  </si>
+  <si>
+    <t>Boys Shoes</t>
+  </si>
+  <si>
+    <t>Ankle Style</t>
   </si>
 </sst>
 </file>
@@ -2821,4 +2901,1660 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C221A2-B7E1-41BA-B044-44C14888F513}">
+  <dimension ref="A1:D82"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>146</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>138</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" t="s">
+        <v>140</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>138</v>
+      </c>
+      <c r="B51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>155</v>
+      </c>
+      <c r="B55" t="s">
+        <v>156</v>
+      </c>
+      <c r="C55" t="s">
+        <v>140</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>158</v>
+      </c>
+      <c r="C57" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>159</v>
+      </c>
+      <c r="C58" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>138</v>
+      </c>
+      <c r="B59" t="s">
+        <v>160</v>
+      </c>
+      <c r="C59" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" t="s">
+        <v>161</v>
+      </c>
+      <c r="C61" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" t="s">
+        <v>111</v>
+      </c>
+      <c r="C62" t="s">
+        <v>140</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" t="s">
+        <v>162</v>
+      </c>
+      <c r="C63" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" t="s">
+        <v>140</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>101</v>
+      </c>
+      <c r="C67" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>117</v>
+      </c>
+      <c r="C68" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>118</v>
+      </c>
+      <c r="C69" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>120</v>
+      </c>
+      <c r="C71" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>121</v>
+      </c>
+      <c r="C72" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>122</v>
+      </c>
+      <c r="C73" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>124</v>
+      </c>
+      <c r="C75" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
+        <v>125</v>
+      </c>
+      <c r="C76" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>126</v>
+      </c>
+      <c r="C77" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>127</v>
+      </c>
+      <c r="C78" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>128</v>
+      </c>
+      <c r="C79" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>130</v>
+      </c>
+      <c r="C81" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>131</v>
+      </c>
+      <c r="C82" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6B29827-7CC1-4B42-82A8-1ED9819A4406}">
+  <dimension ref="A1:D82"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>146</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>138</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>138</v>
+      </c>
+      <c r="B51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" t="s">
+        <v>163</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>155</v>
+      </c>
+      <c r="B55" t="s">
+        <v>156</v>
+      </c>
+      <c r="C55" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" t="s">
+        <v>163</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" t="s">
+        <v>160</v>
+      </c>
+      <c r="C58" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>138</v>
+      </c>
+      <c r="B60" t="s">
+        <v>161</v>
+      </c>
+      <c r="C60" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" t="s">
+        <v>162</v>
+      </c>
+      <c r="C62" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>111</v>
+      </c>
+      <c r="C63" t="s">
+        <v>163</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" t="s">
+        <v>163</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>101</v>
+      </c>
+      <c r="C67" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>117</v>
+      </c>
+      <c r="C68" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>118</v>
+      </c>
+      <c r="C69" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>120</v>
+      </c>
+      <c r="C71" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>121</v>
+      </c>
+      <c r="C72" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>122</v>
+      </c>
+      <c r="C73" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>124</v>
+      </c>
+      <c r="C75" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
+        <v>125</v>
+      </c>
+      <c r="C76" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>126</v>
+      </c>
+      <c r="C77" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>127</v>
+      </c>
+      <c r="C78" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>128</v>
+      </c>
+      <c r="C79" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>130</v>
+      </c>
+      <c r="C81" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>131</v>
+      </c>
+      <c r="C82" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/config/Ajio_instruction.xlsx
+++ b/config/Ajio_instruction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD88CE17-3FD8-44C7-9504-3727ED755357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64F1D60-60C4-47BE-BCE7-4A090BD400A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="3" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="2" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping-Tshirts" sheetId="7" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="Mapping-Boys Shoes" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mapping-Boys Sandal'!$A$1:$D$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Mapping-Boys Shoes'!$A$1:$D$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Kids Tshirts'!$A$1:$F$89</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -3012,7 +3014,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>51</v>
@@ -3023,7 +3025,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>52</v>
@@ -3034,7 +3036,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
         <v>53</v>
@@ -3045,7 +3047,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>54</v>
@@ -3067,7 +3069,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
@@ -3078,7 +3080,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
@@ -3089,7 +3091,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
         <v>58</v>
@@ -3100,7 +3102,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
         <v>59</v>
@@ -3111,7 +3113,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
         <v>60</v>
@@ -3122,7 +3124,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
         <v>61</v>
@@ -3133,7 +3135,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
         <v>62</v>
@@ -3144,7 +3146,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
         <v>63</v>
@@ -3155,7 +3157,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
         <v>64</v>
@@ -3166,7 +3168,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
         <v>65</v>
@@ -3177,7 +3179,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
         <v>66</v>
@@ -3188,7 +3190,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>67</v>
@@ -3239,7 +3241,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
         <v>71</v>
@@ -3294,7 +3296,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
         <v>83</v>
@@ -3356,7 +3358,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B44" t="s">
         <v>78</v>
@@ -3424,7 +3426,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B51" t="s">
         <v>151</v>
@@ -3509,7 +3511,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B59" t="s">
         <v>160</v>
@@ -3528,7 +3530,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B61" t="s">
         <v>161</v>
@@ -3553,7 +3555,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B63" t="s">
         <v>162</v>
@@ -3564,7 +3566,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B64" t="s">
         <v>105</v>
@@ -3575,7 +3577,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B65" t="s">
         <v>96</v>
@@ -3837,7 +3839,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>51</v>
@@ -3848,7 +3850,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>52</v>
@@ -3859,7 +3861,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
         <v>53</v>
@@ -3870,7 +3872,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>54</v>
@@ -3892,7 +3894,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
@@ -3903,7 +3905,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
@@ -3914,7 +3916,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
         <v>58</v>
@@ -3925,7 +3927,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
         <v>59</v>
@@ -3936,7 +3938,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
         <v>60</v>
@@ -3947,7 +3949,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
         <v>61</v>
@@ -3958,7 +3960,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
         <v>62</v>
@@ -3969,7 +3971,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
         <v>63</v>
@@ -3980,7 +3982,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
         <v>64</v>
@@ -3991,7 +3993,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
         <v>65</v>
@@ -4002,7 +4004,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
         <v>66</v>
@@ -4013,7 +4015,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>67</v>
@@ -4064,7 +4066,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
         <v>71</v>
@@ -4119,7 +4121,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
         <v>83</v>
@@ -4181,7 +4183,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B44" t="s">
         <v>78</v>
@@ -4249,7 +4251,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B51" t="s">
         <v>151</v>
@@ -4326,7 +4328,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B58" t="s">
         <v>160</v>
@@ -4345,7 +4347,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B60" t="s">
         <v>161</v>
@@ -4356,7 +4358,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B61" t="s">
         <v>105</v>
@@ -4367,7 +4369,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B62" t="s">
         <v>162</v>
@@ -4392,7 +4394,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B64" t="s">
         <v>164</v>
@@ -4403,7 +4405,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="B65" t="s">
         <v>96</v>

--- a/config/Ajio_instruction.xlsx
+++ b/config/Ajio_instruction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64F1D60-60C4-47BE-BCE7-4A090BD400A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4FBCD0-AB15-4726-A29D-B6B202F72B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="2" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="3" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping-Tshirts" sheetId="7" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="165">
   <si>
     <t>Base file Column</t>
   </si>
@@ -2911,6 +2911,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -3022,6 +3023,9 @@
       <c r="C10" t="s">
         <v>140</v>
       </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -3033,6 +3037,9 @@
       <c r="C11" t="s">
         <v>140</v>
       </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -3044,6 +3051,9 @@
       <c r="C12" t="s">
         <v>140</v>
       </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -3054,6 +3064,9 @@
       </c>
       <c r="C13" t="s">
         <v>140</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -3077,6 +3090,9 @@
       <c r="C15" t="s">
         <v>140</v>
       </c>
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -3088,8 +3104,11 @@
       <c r="C16" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -3099,8 +3118,11 @@
       <c r="C17" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -3110,8 +3132,11 @@
       <c r="C18" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -3121,8 +3146,11 @@
       <c r="C19" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -3132,8 +3160,11 @@
       <c r="C20" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -3143,8 +3174,11 @@
       <c r="C21" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -3154,8 +3188,11 @@
       <c r="C22" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -3165,8 +3202,11 @@
       <c r="C23" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -3176,8 +3216,11 @@
       <c r="C24" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -3187,8 +3230,11 @@
       <c r="C25" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -3198,8 +3244,11 @@
       <c r="C26" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>74</v>
       </c>
@@ -3207,7 +3256,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>73</v>
       </c>
@@ -3215,7 +3264,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>68</v>
       </c>
@@ -3223,7 +3272,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>69</v>
       </c>
@@ -3231,7 +3280,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>70</v>
       </c>
@@ -3239,7 +3288,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -3249,8 +3298,11 @@
       <c r="C32" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>144</v>
       </c>
@@ -3261,7 +3313,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>145</v>
       </c>
@@ -3272,7 +3324,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>146</v>
       </c>
@@ -3283,7 +3335,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>147</v>
       </c>
@@ -3294,7 +3346,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -3304,8 +3356,11 @@
       <c r="C37" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>79</v>
       </c>
@@ -3313,7 +3368,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>85</v>
       </c>
@@ -3321,7 +3376,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>80</v>
       </c>
@@ -3329,7 +3384,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>82</v>
       </c>
@@ -3337,7 +3392,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>81</v>
       </c>
@@ -3345,7 +3400,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>148</v>
       </c>
@@ -3356,7 +3411,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -3366,8 +3421,11 @@
       <c r="C44" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>86</v>
       </c>
@@ -3375,7 +3433,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>87</v>
       </c>
@@ -3383,7 +3441,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>149</v>
       </c>
@@ -3391,7 +3449,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>91</v>
       </c>
@@ -3434,6 +3492,9 @@
       <c r="C51" t="s">
         <v>140</v>
       </c>
+      <c r="D51" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
@@ -3519,6 +3580,9 @@
       <c r="C59" t="s">
         <v>140</v>
       </c>
+      <c r="D59" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
@@ -3538,6 +3602,9 @@
       <c r="C61" t="s">
         <v>140</v>
       </c>
+      <c r="D61" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
@@ -3563,6 +3630,9 @@
       <c r="C63" t="s">
         <v>140</v>
       </c>
+      <c r="D63" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
@@ -3574,6 +3644,9 @@
       <c r="C64" t="s">
         <v>140</v>
       </c>
+      <c r="D64" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
@@ -3584,6 +3657,9 @@
       </c>
       <c r="C65" t="s">
         <v>140</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
@@ -3847,6 +3923,9 @@
       <c r="C10" t="s">
         <v>163</v>
       </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -3858,6 +3937,9 @@
       <c r="C11" t="s">
         <v>163</v>
       </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -3869,6 +3951,9 @@
       <c r="C12" t="s">
         <v>163</v>
       </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -3879,6 +3964,9 @@
       </c>
       <c r="C13" t="s">
         <v>163</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -3902,6 +3990,9 @@
       <c r="C15" t="s">
         <v>163</v>
       </c>
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -3913,8 +4004,11 @@
       <c r="C16" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -3924,8 +4018,11 @@
       <c r="C17" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -3935,8 +4032,11 @@
       <c r="C18" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -3946,8 +4046,11 @@
       <c r="C19" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -3957,8 +4060,11 @@
       <c r="C20" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -3968,8 +4074,11 @@
       <c r="C21" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -3979,8 +4088,11 @@
       <c r="C22" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -3990,8 +4102,11 @@
       <c r="C23" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -4001,8 +4116,11 @@
       <c r="C24" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -4012,8 +4130,11 @@
       <c r="C25" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -4023,8 +4144,11 @@
       <c r="C26" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>74</v>
       </c>
@@ -4032,7 +4156,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>73</v>
       </c>
@@ -4040,7 +4164,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>68</v>
       </c>
@@ -4048,7 +4172,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>69</v>
       </c>
@@ -4056,7 +4180,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>70</v>
       </c>
@@ -4064,7 +4188,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -4074,8 +4198,11 @@
       <c r="C32" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>144</v>
       </c>
@@ -4086,7 +4213,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>145</v>
       </c>
@@ -4097,7 +4224,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>146</v>
       </c>
@@ -4108,7 +4235,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>147</v>
       </c>
@@ -4119,7 +4246,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -4129,8 +4256,11 @@
       <c r="C37" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>79</v>
       </c>
@@ -4138,7 +4268,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>85</v>
       </c>
@@ -4146,7 +4276,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>80</v>
       </c>
@@ -4154,7 +4284,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>82</v>
       </c>
@@ -4162,7 +4292,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>81</v>
       </c>
@@ -4170,7 +4300,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>148</v>
       </c>
@@ -4181,7 +4311,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -4191,8 +4321,11 @@
       <c r="C44" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>86</v>
       </c>
@@ -4200,7 +4333,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>87</v>
       </c>
@@ -4208,7 +4341,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>149</v>
       </c>
@@ -4216,7 +4349,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>91</v>
       </c>
@@ -4259,6 +4392,9 @@
       <c r="C51" t="s">
         <v>163</v>
       </c>
+      <c r="D51" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
@@ -4336,6 +4472,9 @@
       <c r="C58" t="s">
         <v>163</v>
       </c>
+      <c r="D58" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
@@ -4355,6 +4494,9 @@
       <c r="C60" t="s">
         <v>163</v>
       </c>
+      <c r="D60" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
@@ -4366,6 +4508,9 @@
       <c r="C61" t="s">
         <v>163</v>
       </c>
+      <c r="D61" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
@@ -4376,6 +4521,9 @@
       </c>
       <c r="C62" t="s">
         <v>163</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -4402,6 +4550,9 @@
       <c r="C64" t="s">
         <v>163</v>
       </c>
+      <c r="D64" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
@@ -4412,6 +4563,9 @@
       </c>
       <c r="C65" t="s">
         <v>163</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">

--- a/config/Ajio_instruction.xlsx
+++ b/config/Ajio_instruction.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4FBCD0-AB15-4726-A29D-B6B202F72B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3642FBA-7050-40F9-8786-DB765D7906D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="3" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" firstSheet="2" activeTab="5" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping-Tshirts" sheetId="7" r:id="rId1"/>
     <sheet name="Mapping-Kids Tshirts" sheetId="6" r:id="rId2"/>
     <sheet name="Mapping-Boys Sandal" sheetId="8" r:id="rId3"/>
     <sheet name="Mapping-Boys Shoes" sheetId="9" r:id="rId4"/>
+    <sheet name="Mapping-Girls Shoes" sheetId="10" r:id="rId5"/>
+    <sheet name="Mapping-Girls Sandal" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mapping-Boys Sandal'!$A$1:$D$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Mapping-Boys Shoes'!$A$1:$D$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Mapping-Girls Shoes'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Kids Tshirts'!$A$1:$F$89</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="171">
   <si>
     <t>Base file Column</t>
   </si>
@@ -539,6 +542,24 @@
   </si>
   <si>
     <t>Ankle Style</t>
+  </si>
+  <si>
+    <t>Girls Shoes</t>
+  </si>
+  <si>
+    <t>Craft</t>
+  </si>
+  <si>
+    <t>*Ankle Style</t>
+  </si>
+  <si>
+    <t>Toe Shape</t>
+  </si>
+  <si>
+    <t>*standardSize</t>
+  </si>
+  <si>
+    <t>Girls Sandal</t>
   </si>
 </sst>
 </file>
@@ -2912,6 +2933,7 @@
   <cols>
     <col min="1" max="1" width="38.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -4713,4 +4735,1789 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479E7038-2B75-4F86-9BE0-8C1290CA6890}">
+  <dimension ref="A1:D83"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>165</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>146</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" t="s">
+        <v>165</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" t="s">
+        <v>165</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>155</v>
+      </c>
+      <c r="B55" t="s">
+        <v>156</v>
+      </c>
+      <c r="C55" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>157</v>
+      </c>
+      <c r="C57" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>158</v>
+      </c>
+      <c r="C58" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" t="s">
+        <v>167</v>
+      </c>
+      <c r="C59" t="s">
+        <v>165</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" t="s">
+        <v>165</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" t="s">
+        <v>165</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" t="s">
+        <v>161</v>
+      </c>
+      <c r="C62" t="s">
+        <v>165</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
+        <v>168</v>
+      </c>
+      <c r="C63" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" t="s">
+        <v>111</v>
+      </c>
+      <c r="C64" t="s">
+        <v>165</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" t="s">
+        <v>165</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" t="s">
+        <v>165</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
+        <v>169</v>
+      </c>
+      <c r="C67" t="s">
+        <v>165</v>
+      </c>
+      <c r="D67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>101</v>
+      </c>
+      <c r="C68" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>117</v>
+      </c>
+      <c r="C69" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>118</v>
+      </c>
+      <c r="C70" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>119</v>
+      </c>
+      <c r="C71" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>120</v>
+      </c>
+      <c r="C72" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>121</v>
+      </c>
+      <c r="C73" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>122</v>
+      </c>
+      <c r="C74" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>123</v>
+      </c>
+      <c r="C75" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
+        <v>124</v>
+      </c>
+      <c r="C76" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>125</v>
+      </c>
+      <c r="C77" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>126</v>
+      </c>
+      <c r="C78" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>127</v>
+      </c>
+      <c r="C79" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>128</v>
+      </c>
+      <c r="C80" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>129</v>
+      </c>
+      <c r="C81" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>130</v>
+      </c>
+      <c r="C82" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>131</v>
+      </c>
+      <c r="C83" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{479E7038-2B75-4F86-9BE0-8C1290CA6890}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17262F06-34F3-4BAE-8F27-134C8532EAF3}">
+  <dimension ref="A1:D81"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>170</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>146</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
+        <v>170</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" t="s">
+        <v>170</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" t="s">
+        <v>170</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B55" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" t="s">
+        <v>170</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>168</v>
+      </c>
+      <c r="C57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" t="s">
+        <v>156</v>
+      </c>
+      <c r="C58" t="s">
+        <v>170</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" t="s">
+        <v>161</v>
+      </c>
+      <c r="C60" t="s">
+        <v>170</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" t="s">
+        <v>160</v>
+      </c>
+      <c r="C61" t="s">
+        <v>170</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>158</v>
+      </c>
+      <c r="C62" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" t="s">
+        <v>96</v>
+      </c>
+      <c r="C63" t="s">
+        <v>170</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64" t="s">
+        <v>170</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" t="s">
+        <v>169</v>
+      </c>
+      <c r="C65" t="s">
+        <v>170</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
+        <v>101</v>
+      </c>
+      <c r="C66" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>117</v>
+      </c>
+      <c r="C67" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>119</v>
+      </c>
+      <c r="C69" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>120</v>
+      </c>
+      <c r="C70" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>121</v>
+      </c>
+      <c r="C71" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>122</v>
+      </c>
+      <c r="C72" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>123</v>
+      </c>
+      <c r="C73" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>124</v>
+      </c>
+      <c r="C74" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>125</v>
+      </c>
+      <c r="C75" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
+        <v>126</v>
+      </c>
+      <c r="C76" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>128</v>
+      </c>
+      <c r="C78" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>129</v>
+      </c>
+      <c r="C79" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>130</v>
+      </c>
+      <c r="C80" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>131</v>
+      </c>
+      <c r="C81" t="s">
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>